--- a/artfynd/A 34285-2024 artfynd.xlsx
+++ b/artfynd/A 34285-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121143267</v>
       </c>
       <c r="B2" t="n">
-        <v>95618</v>
+        <v>95628</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 34285-2024 artfynd.xlsx
+++ b/artfynd/A 34285-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121143267</v>
       </c>
       <c r="B2" t="n">
-        <v>95628</v>
+        <v>95641</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 34285-2024 artfynd.xlsx
+++ b/artfynd/A 34285-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121143267</v>
       </c>
       <c r="B2" t="n">
-        <v>95641</v>
+        <v>95642</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 34285-2024 artfynd.xlsx
+++ b/artfynd/A 34285-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121143267</v>
       </c>
       <c r="B2" t="n">
-        <v>95642</v>
+        <v>95645</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 34285-2024 artfynd.xlsx
+++ b/artfynd/A 34285-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>121143267</v>
       </c>
       <c r="B2" t="n">
-        <v>95645</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,6 +778,432 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>121143262</v>
+      </c>
+      <c r="B3" t="n">
+        <v>4781</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Hallsberg-Laxå, Nrk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>483325</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6539838</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2023-10-05</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2023-10-05</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>kläckhål och/eller gnag</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>121143263</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hallsberg-Laxå, Nrk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>483311</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6539781</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-10-05</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-10-05</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121143265</v>
+      </c>
+      <c r="B5" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hallsberg-Laxå, Nrk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>483309</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6539770</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-10-05</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-10-05</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>kläckhål och/eller gnag</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>130061531</v>
+      </c>
+      <c r="B6" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Sågen, Laxå, Nrk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>483309</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6539817</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34285-2024 artfynd.xlsx
+++ b/artfynd/A 34285-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121143267</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121143262</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -991,6 +1006,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121143263</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1103,6 +1123,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121143265</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1204,8 +1229,20 @@
           <t>Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130061531</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>